--- a/backend/benchmark_data/demo_deal/t12/maple_ridge_t12.xlsx
+++ b/backend/benchmark_data/demo_deal/t12/maple_ridge_t12.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +32,20 @@
       <sz val="14"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="4">
@@ -57,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,21 +76,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -485,1425 +525,1559 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Line Item</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Sep-25</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Oct-25</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Nov-25</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Dec-25</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Jan-26</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Feb-26</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Mar-26</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Apr-26</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>May-26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Jun-26</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Aug-26</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Prepared 09/02/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Annual Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Gross Potential Rent</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2177280</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Vacancy Loss</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>-107685.39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Loss to Lease</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-25521.97</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Net Rental Income Billed</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2044072.64</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Concessions</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>-11200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Bad Debt / Collection Loss</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>-122562</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Total Rent Collected</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1910310.64</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Total Other Income</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>86340.27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>1996650.91</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>766762.83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>NET OPERATING INCOME (NOI)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>1229888.08</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Bad Debt as % of Net Rental Income Billed</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Sep-25</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Oct-25</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Nov-25</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Dec-25</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Jan-26</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
           <t>INCOME</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Gross Potential Rent</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="L22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="M22" s="13" t="n">
         <v>181440</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N22" s="14" t="n">
         <v>2177280</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Vacancy Loss</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B23" s="13" t="n">
         <v>-8750.870000000001</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C23" s="13" t="n">
         <v>-8638.25</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D23" s="13" t="n">
         <v>-8834.85</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E23" s="13" t="n">
         <v>-8620.73</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F23" s="13" t="n">
         <v>-8611.280000000001</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G23" s="13" t="n">
         <v>-9503.459999999999</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H23" s="13" t="n">
         <v>-9484.02</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I23" s="13" t="n">
         <v>-9024.889999999999</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J23" s="13" t="n">
         <v>-8575.9</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="K23" s="13" t="n">
         <v>-8966.5</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L23" s="13" t="n">
         <v>-9453.469999999999</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="M23" s="13" t="n">
         <v>-9221.17</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="N23" s="14" t="n">
         <v>-107685.39</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Loss to Lease</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B24" s="13" t="n">
         <v>-2169.32</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C24" s="13" t="n">
         <v>-2201.66</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D24" s="13" t="n">
         <v>-2068.84</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E24" s="13" t="n">
         <v>-2070.35</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F24" s="13" t="n">
         <v>-2247.19</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G24" s="13" t="n">
         <v>-2228.19</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H24" s="13" t="n">
         <v>-2183.54</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I24" s="13" t="n">
         <v>-2114.61</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J24" s="13" t="n">
         <v>-2062.01</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K24" s="13" t="n">
         <v>-2095.49</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L24" s="13" t="n">
         <v>-2022.25</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M24" s="13" t="n">
         <v>-2058.52</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N24" s="14" t="n">
         <v>-25521.97</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Net Rental Income Billed (ties to current rent roll)</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B25" s="14" t="n">
         <v>170519.81</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C25" s="14" t="n">
         <v>170600.09</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D25" s="14" t="n">
         <v>170536.31</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E25" s="14" t="n">
         <v>170748.92</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F25" s="14" t="n">
         <v>170581.53</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G25" s="14" t="n">
         <v>169708.35</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H25" s="14" t="n">
         <v>169772.44</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I25" s="14" t="n">
         <v>170300.5</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J25" s="14" t="n">
         <v>170802.09</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K25" s="14" t="n">
         <v>170378.01</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L25" s="14" t="n">
         <v>169964.28</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="M25" s="14" t="n">
         <v>170160.31</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="N25" s="14" t="n">
         <v>2044072.64</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Concessions</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B26" s="13" t="n">
         <v>-879.52</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C26" s="13" t="n">
         <v>-1119.9</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D26" s="13" t="n">
         <v>-617.9400000000001</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E26" s="13" t="n">
         <v>-1040.95</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F26" s="13" t="n">
         <v>-1238.16</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G26" s="13" t="n">
         <v>-709.92</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H26" s="13" t="n">
         <v>-788.76</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I26" s="13" t="n">
         <v>-1362.88</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J26" s="13" t="n">
         <v>-1339.88</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="K26" s="13" t="n">
         <v>-1113.99</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="L26" s="13" t="n">
         <v>-1306.7</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="M26" s="13" t="n">
         <v>318.6</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N26" s="14" t="n">
         <v>-11200</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Bad Debt / Collection Loss</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B27" s="13" t="n">
         <v>-10261.76</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C27" s="13" t="n">
         <v>-10601.18</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D27" s="13" t="n">
         <v>-10060.91</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E27" s="13" t="n">
         <v>-10322.55</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F27" s="13" t="n">
         <v>-10030.3</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G27" s="13" t="n">
         <v>-10452.95</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H27" s="13" t="n">
         <v>-10745.76</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I27" s="13" t="n">
         <v>-10075.56</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J27" s="13" t="n">
         <v>-9973.110000000001</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="K27" s="13" t="n">
         <v>-10111.32</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="L27" s="13" t="n">
         <v>-10490.77</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="M27" s="13" t="n">
         <v>-9435.83</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N27" s="14" t="n">
         <v>-122562</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Total Rent Collected</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B28" s="14" t="n">
         <v>159378.53</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C28" s="14" t="n">
         <v>158879.01</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D28" s="14" t="n">
         <v>159857.46</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E28" s="14" t="n">
         <v>159385.42</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F28" s="14" t="n">
         <v>159313.07</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G28" s="14" t="n">
         <v>158545.48</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H28" s="14" t="n">
         <v>158237.92</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I28" s="14" t="n">
         <v>158862.06</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J28" s="14" t="n">
         <v>159489.1</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K28" s="14" t="n">
         <v>159152.7</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L28" s="14" t="n">
         <v>158166.81</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="M28" s="14" t="n">
         <v>161043.08</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="N28" s="14" t="n">
         <v>1910310.64</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="11" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Utility Reimbursement (RUBS)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B31" s="13" t="n">
         <v>4341.89</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C31" s="13" t="n">
         <v>4111.39</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D31" s="13" t="n">
         <v>4364.99</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E31" s="13" t="n">
         <v>4007.54</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F31" s="13" t="n">
         <v>4258.95</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G31" s="13" t="n">
         <v>4426.79</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H31" s="13" t="n">
         <v>3986.74</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I31" s="13" t="n">
         <v>4119.64</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J31" s="13" t="n">
         <v>4224.64</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="K31" s="13" t="n">
         <v>4201.46</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="L31" s="13" t="n">
         <v>4133.93</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="M31" s="13" t="n">
         <v>4102.21</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N31" s="14" t="n">
         <v>50280.17</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Application &amp; Administrative Fees</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B32" s="13" t="n">
         <v>886.88</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C32" s="13" t="n">
         <v>804.72</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D32" s="13" t="n">
         <v>855.58</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E32" s="13" t="n">
         <v>833.84</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F32" s="13" t="n">
         <v>818.1900000000001</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G32" s="13" t="n">
         <v>870.04</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H32" s="13" t="n">
         <v>847.0599999999999</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I32" s="13" t="n">
         <v>824.6799999999999</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J32" s="13" t="n">
         <v>893.15</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="K32" s="13" t="n">
         <v>814.29</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="L32" s="13" t="n">
         <v>860.16</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="M32" s="13" t="n">
         <v>886.59</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N32" s="14" t="n">
         <v>10195.18</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Pet Rent &amp; Fees</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B33" s="13" t="n">
         <v>877.65</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C33" s="13" t="n">
         <v>951.01</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D33" s="13" t="n">
         <v>870.76</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E33" s="13" t="n">
         <v>918.88</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F33" s="13" t="n">
         <v>920.9400000000001</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G33" s="13" t="n">
         <v>880.7</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H33" s="13" t="n">
         <v>927.55</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I33" s="13" t="n">
         <v>913.4400000000001</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J33" s="13" t="n">
         <v>912.1</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="K33" s="13" t="n">
         <v>878.26</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="L33" s="13" t="n">
         <v>854.49</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="M33" s="13" t="n">
         <v>925.16</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N33" s="14" t="n">
         <v>10830.94</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Late Fees</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B34" s="13" t="n">
         <v>563.7</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C34" s="13" t="n">
         <v>530.6900000000001</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D34" s="13" t="n">
         <v>536.48</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E34" s="13" t="n">
         <v>525.5700000000001</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F34" s="13" t="n">
         <v>566.3200000000001</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G34" s="13" t="n">
         <v>551.8</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H34" s="13" t="n">
         <v>526.5</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I34" s="13" t="n">
         <v>553.7</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="J34" s="13" t="n">
         <v>542.97</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="K34" s="13" t="n">
         <v>570.26</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="L34" s="13" t="n">
         <v>562.4299999999999</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="M34" s="13" t="n">
         <v>573.4</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N34" s="14" t="n">
         <v>6603.82</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Parking &amp; Storage Income</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B35" s="13" t="n">
         <v>401.32</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C35" s="13" t="n">
         <v>391.41</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D35" s="13" t="n">
         <v>382.23</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E35" s="13" t="n">
         <v>406.43</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F35" s="13" t="n">
         <v>408.28</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G35" s="13" t="n">
         <v>393.94</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H35" s="13" t="n">
         <v>409.34</v>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I35" s="13" t="n">
         <v>385.42</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J35" s="13" t="n">
         <v>390.81</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="K35" s="13" t="n">
         <v>421.81</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="L35" s="13" t="n">
         <v>408.68</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="M35" s="13" t="n">
         <v>409.6</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N35" s="14" t="n">
         <v>4809.27</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Other / Miscellaneous Income</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B36" s="13" t="n">
         <v>282.72</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C36" s="13" t="n">
         <v>317.39</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D36" s="13" t="n">
         <v>286.89</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E36" s="13" t="n">
         <v>304.93</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F36" s="13" t="n">
         <v>308.47</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G36" s="13" t="n">
         <v>301.18</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H36" s="13" t="n">
         <v>302.92</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I36" s="13" t="n">
         <v>292.82</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="J36" s="13" t="n">
         <v>289.13</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="K36" s="13" t="n">
         <v>315.43</v>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="L36" s="13" t="n">
         <v>303.09</v>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="M36" s="13" t="n">
         <v>315.92</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N36" s="14" t="n">
         <v>3620.89</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Total Other Income</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B37" s="14" t="n">
         <v>7354.16</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C37" s="14" t="n">
         <v>7106.61</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D37" s="14" t="n">
         <v>7296.93</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E37" s="14" t="n">
         <v>6997.19</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F37" s="14" t="n">
         <v>7281.15</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G37" s="14" t="n">
         <v>7424.45</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H37" s="14" t="n">
         <v>7000.11</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I37" s="14" t="n">
         <v>7089.7</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J37" s="14" t="n">
         <v>7252.8</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K37" s="14" t="n">
         <v>7201.51</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L37" s="14" t="n">
         <v>7122.78</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M37" s="14" t="n">
         <v>7212.88</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N37" s="14" t="n">
         <v>86340.27</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>TOTAL INCOME</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B38" s="14" t="n">
         <v>166732.69</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C38" s="14" t="n">
         <v>165985.62</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D38" s="14" t="n">
         <v>167154.39</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E38" s="14" t="n">
         <v>166382.61</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F38" s="14" t="n">
         <v>166594.22</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G38" s="14" t="n">
         <v>165969.93</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H38" s="14" t="n">
         <v>165238.03</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I38" s="14" t="n">
         <v>165951.76</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J38" s="14" t="n">
         <v>166741.9</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="K38" s="14" t="n">
         <v>166354.21</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="L38" s="14" t="n">
         <v>165289.59</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="M38" s="14" t="n">
         <v>168255.96</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N38" s="14" t="n">
         <v>1996650.91</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="11" t="n"/>
+      <c r="N39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>OPERATING EXPENSES</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="11" t="n"/>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="11" t="n"/>
+      <c r="N40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Payroll &amp; Benefits</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B41" s="13" t="n">
         <v>11513.4</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C41" s="13" t="n">
         <v>11359.45</v>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D41" s="13" t="n">
         <v>11329.44</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E41" s="13" t="n">
         <v>11881.19</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F41" s="13" t="n">
         <v>11193.44</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G41" s="13" t="n">
         <v>11056.71</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H41" s="13" t="n">
         <v>11662.09</v>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="I41" s="13" t="n">
         <v>11537.14</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="J41" s="13" t="n">
         <v>11980.02</v>
       </c>
-      <c r="K26" s="5" t="n">
+      <c r="K41" s="13" t="n">
         <v>10846.82</v>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="L41" s="13" t="n">
         <v>11263.46</v>
       </c>
-      <c r="M26" s="5" t="n">
+      <c r="M41" s="13" t="n">
         <v>11921.77</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N41" s="14" t="n">
         <v>137544.93</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B42" s="13" t="n">
         <v>7662.11</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C42" s="13" t="n">
         <v>7858.17</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D42" s="13" t="n">
         <v>7945.74</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E42" s="13" t="n">
         <v>8275.059999999999</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F42" s="13" t="n">
         <v>7579.42</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G42" s="13" t="n">
         <v>8409.4</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H42" s="13" t="n">
         <v>8104.89</v>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="I42" s="13" t="n">
         <v>7565.39</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J42" s="13" t="n">
         <v>8129.56</v>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="K42" s="13" t="n">
         <v>7787.96</v>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="L42" s="13" t="n">
         <v>8401.860000000001</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="M42" s="13" t="n">
         <v>7808.75</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N42" s="14" t="n">
         <v>95528.31</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Turnover / Make-Ready</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B43" s="13" t="n">
         <v>3537.02</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C43" s="13" t="n">
         <v>3967.59</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D43" s="13" t="n">
         <v>3614.11</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E43" s="13" t="n">
         <v>3956.15</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F43" s="13" t="n">
         <v>3637.03</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="G43" s="13" t="n">
         <v>3957.89</v>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H43" s="13" t="n">
         <v>3726.19</v>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="I43" s="13" t="n">
         <v>3881.38</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="J43" s="13" t="n">
         <v>3705.54</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="K43" s="13" t="n">
         <v>3738.01</v>
       </c>
-      <c r="L28" s="5" t="n">
+      <c r="L43" s="13" t="n">
         <v>3724.66</v>
       </c>
-      <c r="M28" s="5" t="n">
+      <c r="M43" s="13" t="n">
         <v>3732.81</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N43" s="14" t="n">
         <v>45178.38</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Contract Services (Landscaping, Pest, Trash, Pool)</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B44" s="13" t="n">
         <v>3997.05</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C44" s="13" t="n">
         <v>3847.9</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D44" s="13" t="n">
         <v>4157.33</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E44" s="13" t="n">
         <v>3936.94</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F44" s="13" t="n">
         <v>3767.49</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G44" s="13" t="n">
         <v>4017.92</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H44" s="13" t="n">
         <v>4052.54</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I44" s="13" t="n">
         <v>3937.43</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J44" s="13" t="n">
         <v>4222.58</v>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="K44" s="13" t="n">
         <v>4224.99</v>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="L44" s="13" t="n">
         <v>4111.83</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="M44" s="13" t="n">
         <v>4110.77</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="N44" s="14" t="n">
         <v>48384.77</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Utilities (Common Area)</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B45" s="13" t="n">
         <v>2849.73</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C45" s="13" t="n">
         <v>2936.7</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D45" s="13" t="n">
         <v>2843.47</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E45" s="13" t="n">
         <v>2889.6</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F45" s="13" t="n">
         <v>2861.88</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="G45" s="13" t="n">
         <v>2954.25</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H45" s="13" t="n">
         <v>3012.46</v>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="I45" s="13" t="n">
         <v>3005.54</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="J45" s="13" t="n">
         <v>2860.48</v>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="K45" s="13" t="n">
         <v>3113.78</v>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="L45" s="13" t="n">
         <v>2987.43</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="M45" s="13" t="n">
         <v>2961.09</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N45" s="14" t="n">
         <v>35276.41</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Marketing &amp; Leasing</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B46" s="13" t="n">
         <v>1978.55</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C46" s="13" t="n">
         <v>2026.04</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D46" s="13" t="n">
         <v>1959.28</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E46" s="13" t="n">
         <v>1888.36</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F46" s="13" t="n">
         <v>1953.53</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="G46" s="13" t="n">
         <v>2021.75</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H46" s="13" t="n">
         <v>2044.28</v>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="I46" s="13" t="n">
         <v>1981.83</v>
       </c>
-      <c r="J31" s="5" t="n">
+      <c r="J46" s="13" t="n">
         <v>2005.68</v>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="K46" s="13" t="n">
         <v>2035.56</v>
       </c>
-      <c r="L31" s="5" t="n">
+      <c r="L46" s="13" t="n">
         <v>2006.88</v>
       </c>
-      <c r="M31" s="5" t="n">
+      <c r="M46" s="13" t="n">
         <v>1943.56</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N46" s="14" t="n">
         <v>23845.3</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>General &amp; Administrative</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B47" s="13" t="n">
         <v>2501.13</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C47" s="13" t="n">
         <v>2553.61</v>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D47" s="13" t="n">
         <v>2633.89</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E47" s="13" t="n">
         <v>2393.62</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F47" s="13" t="n">
         <v>2414.77</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G47" s="13" t="n">
         <v>2436.47</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H47" s="13" t="n">
         <v>2516.35</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I47" s="13" t="n">
         <v>2572.81</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="J47" s="13" t="n">
         <v>2535.48</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="K47" s="13" t="n">
         <v>2382.8</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="L47" s="13" t="n">
         <v>2475.69</v>
       </c>
-      <c r="M32" s="5" t="n">
+      <c r="M47" s="13" t="n">
         <v>2597.82</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="N47" s="14" t="n">
         <v>30014.44</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B48" s="13" t="n">
         <v>5208.64</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C48" s="13" t="n">
         <v>5088.96</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D48" s="13" t="n">
         <v>5441.42</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E48" s="13" t="n">
         <v>4984.51</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F48" s="13" t="n">
         <v>4997.89</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G48" s="13" t="n">
         <v>5005.59</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H48" s="13" t="n">
         <v>5509.94</v>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I48" s="13" t="n">
         <v>5475.51</v>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="J48" s="13" t="n">
         <v>5309.99</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="K48" s="13" t="n">
         <v>5235.64</v>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="L48" s="13" t="n">
         <v>5067.17</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="M48" s="13" t="n">
         <v>5267.12</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N48" s="14" t="n">
         <v>62592.38</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Property Taxes (Dallas County / TX)</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B49" s="13" t="n">
         <v>19931.87</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C49" s="13" t="n">
         <v>19512.84</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D49" s="13" t="n">
         <v>18601.89</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E49" s="13" t="n">
         <v>18357.15</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F49" s="13" t="n">
         <v>18462.22</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G49" s="13" t="n">
         <v>18831.75</v>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H49" s="13" t="n">
         <v>19754.83</v>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="I49" s="13" t="n">
         <v>17955.66</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="J49" s="13" t="n">
         <v>19771.28</v>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="K49" s="13" t="n">
         <v>19117.26</v>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="L49" s="13" t="n">
         <v>18194.5</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="M49" s="13" t="n">
         <v>20007.12</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="N49" s="14" t="n">
         <v>228498.37</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Management Fee (3% of Total Income)</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B50" s="13" t="n">
         <v>5001.98</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C50" s="13" t="n">
         <v>4979.57</v>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D50" s="13" t="n">
         <v>5014.63</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E50" s="13" t="n">
         <v>4991.48</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F50" s="13" t="n">
         <v>4997.83</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G50" s="13" t="n">
         <v>4979.1</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H50" s="13" t="n">
         <v>4957.14</v>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="I50" s="13" t="n">
         <v>4978.55</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J50" s="13" t="n">
         <v>5002.26</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="K50" s="13" t="n">
         <v>4990.63</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="L50" s="13" t="n">
         <v>4958.69</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="M50" s="13" t="n">
         <v>5047.68</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N50" s="14" t="n">
         <v>59899.54</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>TOTAL OPERATING EXPENSES</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B51" s="14" t="n">
         <v>64181.48</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C51" s="14" t="n">
         <v>64130.83</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D51" s="14" t="n">
         <v>63541.2</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E51" s="14" t="n">
         <v>63554.06</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F51" s="14" t="n">
         <v>61865.5</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G51" s="14" t="n">
         <v>63670.83</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H51" s="14" t="n">
         <v>65340.71</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I51" s="14" t="n">
         <v>62891.24</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J51" s="14" t="n">
         <v>65522.87</v>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="K51" s="14" t="n">
         <v>63473.45</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="L51" s="14" t="n">
         <v>63192.17</v>
       </c>
-      <c r="M36" s="6" t="n">
+      <c r="M51" s="14" t="n">
         <v>65398.49</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N51" s="14" t="n">
         <v>766762.83</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
-      <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="11" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="11" t="n"/>
+      <c r="K52" s="11" t="n"/>
+      <c r="L52" s="11" t="n"/>
+      <c r="M52" s="11" t="n"/>
+      <c r="N52" s="11" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>NET OPERATING INCOME (NOI)</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B53" s="14" t="n">
         <v>102551.21</v>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="C53" s="14" t="n">
         <v>101854.79</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D53" s="14" t="n">
         <v>103613.19</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E53" s="14" t="n">
         <v>102828.55</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F53" s="14" t="n">
         <v>104728.72</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G53" s="14" t="n">
         <v>102299.1</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H53" s="14" t="n">
         <v>99897.32000000001</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I53" s="14" t="n">
         <v>103060.52</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J53" s="14" t="n">
         <v>101219.03</v>
       </c>
-      <c r="K38" s="6" t="n">
+      <c r="K53" s="14" t="n">
         <v>102880.76</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="L53" s="14" t="n">
         <v>102097.42</v>
       </c>
-      <c r="M38" s="6" t="n">
+      <c r="M53" s="14" t="n">
         <v>102857.47</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="N53" s="14" t="n">
         <v>1229888.08</v>
       </c>
     </row>

--- a/backend/benchmark_data/demo_deal/t12/maple_ridge_t12.xlsx
+++ b/backend/benchmark_data/demo_deal/t12/maple_ridge_t12.xlsx
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>September 2025 through August 2026</t>
+          <t>October 2025 through September 2026</t>
         </is>
       </c>
     </row>
@@ -493,62 +493,62 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Sep-25</t>
+          <t>Oct-25</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Oct-25</t>
+          <t>Nov-25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Nov-25</t>
+          <t>Dec-25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dec-25</t>
+          <t>Jan-26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Jan-26</t>
+          <t>Feb-26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Feb-26</t>
+          <t>Mar-26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Apr-26</t>
+          <t>May-26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>May-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>Jul-26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Jul-26</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
